--- a/data/formations-suivi-inscriptions.xlsx
+++ b/data/formations-suivi-inscriptions.xlsx
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -154,9 +154,6 @@
     </xf>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1">
       <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -676,7 +673,7 @@
     <col min="6" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
+    <row r="1" ht="16.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -693,7 +690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="14.25">
+    <row r="2" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -710,7 +707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="14.25">
+    <row r="3" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -727,7 +724,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" ht="14.25">
+    <row r="4" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -744,7 +741,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" ht="14.25">
+    <row r="5" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -761,7 +758,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" ht="14.25">
+    <row r="6" ht="16.5">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -778,7 +775,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="14.25">
+    <row r="7" ht="16.5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,7 +792,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" ht="14.25">
+    <row r="8" ht="16.5">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,9 +805,11 @@
       <c r="D8" s="7">
         <v>250</v>
       </c>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" ht="14.25">
+      <c r="E8" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -827,7 +826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
+    <row r="10" ht="16.5">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -844,7 +843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
+    <row r="11" ht="16.5">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,7 +860,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
+    <row r="12" ht="16.5">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,7 +877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="14.25">
+    <row r="13" ht="16.5">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -892,10 +891,10 @@
         <v>350</v>
       </c>
       <c r="E13" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,10 +908,10 @@
         <v>150</v>
       </c>
       <c r="E14" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -929,7 +928,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" ht="14.25">
+    <row r="16" ht="16.5">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
@@ -942,9 +941,11 @@
       <c r="D16" s="7">
         <v>250</v>
       </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" ht="14.25">
+      <c r="E16" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -961,7 +962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" ht="14.25">
+    <row r="18" ht="16.5">
       <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
@@ -978,7 +979,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" ht="14.25">
+    <row r="19" ht="16.5">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -992,10 +993,10 @@
         <v>150</v>
       </c>
       <c r="E19" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1008,9 +1009,11 @@
       <c r="D20" s="7">
         <v>250</v>
       </c>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" ht="14.25">
+      <c r="E20" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5">
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1023,13 +1026,60 @@
       <c r="D21" s="7">
         <v>250</v>
       </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="3"/>
+      <c r="E21" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="7">
+        <v>250</v>
+      </c>
+      <c r="E22" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="7">
+        <v>150</v>
+      </c>
+      <c r="E23" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="7">
+        <v>150</v>
+      </c>
+      <c r="E24" s="3">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1241,9 +1291,7 @@
         <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
         <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
           <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
+            <xsd:documentation>This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.</xsd:documentation>
           </xsd:annotation>
         </xsd:element>
         <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1322,13 +1370,41 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8899008-0902-487F-8AD9-96D6E33BEE3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8899008-0902-487F-8AD9-96D6E33BEE3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e8aa3a5b-f132-49e0-8c16-b529a19cb925"/>
+    <ds:schemaRef ds:uri="d00851a3-98d5-4895-85b0-064e2216f632"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95BF5E31-36B9-46D7-93FB-144A89CF3CE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95BF5E31-36B9-46D7-93FB-144A89CF3CE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8AF860E-CB0A-4E25-8A80-03908EE4B437}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8AF860E-CB0A-4E25-8A80-03908EE4B437}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d00851a3-98d5-4895-85b0-064e2216f632"/>
+    <ds:schemaRef ds:uri="e8aa3a5b-f132-49e0-8c16-b529a19cb925"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>